--- a/docs/Registro_Defectos_Ferramas.xlsx
+++ b/docs/Registro_Defectos_Ferramas.xlsx
@@ -716,7 +716,7 @@
       <c r="D5" s="19" t="n"/>
       <c r="E5" s="17" t="inlineStr">
         <is>
-          <t>Fitzroyal</t>
+          <t>Jose Larenas</t>
         </is>
       </c>
       <c r="F5" s="18" t="n"/>
@@ -735,7 +735,7 @@
       <c r="D6" s="19" t="n"/>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t>Fitzroyal</t>
+          <t>Oscar Oviedo</t>
         </is>
       </c>
       <c r="F6" s="18" t="n"/>
@@ -754,7 +754,7 @@
       <c r="D7" s="19" t="n"/>
       <c r="E7" s="17" t="inlineStr">
         <is>
-          <t>Equipo Ferramas</t>
+          <t>Equipo Ferramas (Jose Larenas, Oscar Oviedo)</t>
         </is>
       </c>
       <c r="F7" s="18" t="n"/>
